--- a/data/gravel/Bearclaw Honey Badger 2025.xlsx
+++ b/data/gravel/Bearclaw Honey Badger 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3E5B78-4CE7-7440-9420-68D41F30ADEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF20553-2A13-4248-B8D9-ECEE7E34D89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="1300" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="1300" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -293,9 +293,6 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>a8:i32</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -402,6 +399,18 @@
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0850/1320/1198/files/Honey_Badger_Titanium_Drop-Bar_Mountain_Bike_profile.jpg?v=1763689288</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:i34</t>
+  </si>
+  <si>
+    <t>100-120</t>
   </si>
 </sst>
 </file>
@@ -754,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -773,7 +782,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -797,12 +806,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -810,7 +819,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -818,7 +827,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="4">
         <v>50</v>
@@ -847,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4">
         <v>535</v>
@@ -992,7 +1001,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4">
         <v>616</v>
@@ -1108,7 +1117,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="4">
         <v>483</v>
@@ -1132,7 +1141,7 @@
         <v>483</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
@@ -1140,7 +1149,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="4">
         <v>44</v>
@@ -1169,7 +1178,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C20" s="4">
         <v>601</v>
@@ -1227,7 +1236,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="4">
         <v>767</v>
@@ -1256,7 +1265,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C23" s="4">
         <v>70</v>
@@ -1285,7 +1294,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24">
         <f>J24*10</f>
@@ -1342,7 +1351,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4">
         <v>160</v>
@@ -1367,551 +1376,605 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="4">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4">
+        <v>100</v>
+      </c>
+      <c r="F26" s="4">
+        <v>100</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="4">
+        <v>100</v>
+      </c>
+      <c r="I26" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
         <v>20</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>24</v>
+      <c r="D27" s="4">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4">
+        <v>20</v>
+      </c>
+      <c r="F27" s="4">
+        <v>20</v>
+      </c>
+      <c r="G27" s="4">
+        <v>20</v>
+      </c>
+      <c r="H27" s="4">
+        <v>20</v>
+      </c>
+      <c r="I27" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
-      <c r="G28">
-        <v>700</v>
-      </c>
-      <c r="H28">
-        <v>700</v>
-      </c>
-      <c r="I28">
-        <v>700</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29">
-        <v>2.4</v>
-      </c>
-      <c r="D29">
-        <v>2.4</v>
-      </c>
-      <c r="E29">
-        <v>2.4</v>
-      </c>
-      <c r="F29">
-        <v>2.4</v>
-      </c>
-      <c r="G29">
-        <v>2.4</v>
-      </c>
-      <c r="H29">
-        <v>2.4</v>
-      </c>
-      <c r="I29">
-        <v>2.4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="G30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="H30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="I30">
-        <v>2.6</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>2.4</v>
+      </c>
+      <c r="D31">
+        <v>2.4</v>
+      </c>
+      <c r="E31">
+        <v>2.4</v>
+      </c>
+      <c r="F31">
+        <v>2.4</v>
+      </c>
+      <c r="G31">
+        <v>2.4</v>
+      </c>
+      <c r="H31">
+        <v>2.4</v>
+      </c>
+      <c r="I31">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32">
+        <v>2.6</v>
+      </c>
+      <c r="D32">
+        <v>2.6</v>
+      </c>
+      <c r="E32">
+        <v>2.6</v>
+      </c>
+      <c r="F32">
+        <v>2.6</v>
+      </c>
+      <c r="G32">
+        <v>2.6</v>
+      </c>
+      <c r="H32">
+        <v>2.6</v>
+      </c>
+      <c r="I32">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:I32" si="1">D33*2.54</f>
+      <c r="D33">
+        <f t="shared" ref="D33:I34" si="1">D35*2.54</f>
         <v>165.1</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>172.72</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="1"/>
         <v>177.8</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <f t="shared" si="1"/>
         <v>182.88</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <f t="shared" si="1"/>
         <v>187.96</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <f t="shared" si="1"/>
         <v>193.04</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <f t="shared" si="1"/>
         <v>175.26</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <f t="shared" si="1"/>
         <v>180.34</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <f t="shared" si="1"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="G32">
+      <c r="G34">
         <f t="shared" si="1"/>
         <v>190.5</v>
       </c>
-      <c r="H32">
+      <c r="H34">
         <f t="shared" si="1"/>
         <v>195.58</v>
       </c>
-      <c r="I32">
+      <c r="I34">
         <f t="shared" si="1"/>
         <v>200.66</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C33">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>64</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>65</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>68</v>
       </c>
-      <c r="F33">
+      <c r="F35">
         <v>70</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>72</v>
       </c>
-      <c r="H33">
+      <c r="H35">
         <v>74</v>
       </c>
-      <c r="I33">
+      <c r="I35">
         <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>67</v>
-      </c>
-      <c r="D34">
-        <v>69</v>
-      </c>
-      <c r="E34">
-        <v>71</v>
-      </c>
-      <c r="F34">
-        <v>73</v>
-      </c>
-      <c r="G34">
-        <v>75</v>
-      </c>
-      <c r="H34">
-        <v>77</v>
-      </c>
-      <c r="I34">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>67</v>
+      </c>
+      <c r="D36">
+        <v>69</v>
+      </c>
+      <c r="E36">
         <v>71</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
+      <c r="F36">
+        <v>73</v>
+      </c>
+      <c r="G36">
+        <v>75</v>
+      </c>
+      <c r="H36">
+        <v>77</v>
+      </c>
+      <c r="I36">
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>74</v>
+        <v>114</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <v>2.6</v>
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>119</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>91</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="B61">
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62">
-        <v>180</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
+      </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="1"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>2490</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>66</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B76" s="1"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>2490</v>
+      </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
         <v>88</v>
-      </c>
-      <c r="B79" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
